--- a/results/mummichog/BC_vs_Control/tables/mcg_pathwayanalysis_BC_vs_Control.xlsx
+++ b/results/mummichog/BC_vs_Control/tables/mcg_pathwayanalysis_BC_vs_Control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="284">
   <si>
     <t>pathway</t>
   </si>
@@ -37,838 +37,835 @@
     <t>overlap_features (name)</t>
   </si>
   <si>
+    <t>Glycosphingolipid metabolism</t>
+  </si>
+  <si>
+    <t>E1436,E350,E1920,E237,E1482,E113,E1431,E652,E236</t>
+  </si>
+  <si>
+    <t>C00249,C00055,C12144,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C06124,C02744,C00588/C05594,C00836,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159</t>
+  </si>
+  <si>
+    <t>Hexadecanoate (n-C16:0)$CMP$Phytosphingosine; 4-D-Hydroxysphinganine$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$Sphingosine 1-phosphate$Psychosine sulfate$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$Sphinganine$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose</t>
+  </si>
+  <si>
     <t>Phosphatidylinositol phosphate metabolism</t>
   </si>
   <si>
-    <t>E238,E351,E239,E1437,E237,E1096,E681</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00055,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00249,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C15658,C01194</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$CMP$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$Hexadecanoate (n-C16:0)$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$6-(alpha-D-Glucosaminyl)-1D-myo-inositol$Phosphatidylinositol</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid metabolism</t>
-  </si>
-  <si>
-    <t>E238,E1483,E239,E1432,E653,E1437,E237,E351,E1921,E113</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C06124,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00588/C05594,C00836,C00249,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00055,C12144,C02744</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$Sphingosine 1-phosphate$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$Sphinganine$Hexadecanoate (n-C16:0)$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$CMP$Phytosphingosine; 4-D-Hydroxysphinganine$Psychosine sulfate</t>
+    <t>E1095,E350,E680,E237,E236,E1436</t>
+  </si>
+  <si>
+    <t>C15658,C00055,C01194,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00249</t>
+  </si>
+  <si>
+    <t>6-(alpha-D-Glucosaminyl)-1D-myo-inositol$CMP$Phosphatidylinositol$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$Hexadecanoate (n-C16:0)</t>
+  </si>
+  <si>
+    <t>Tyrosine metabolism</t>
+  </si>
+  <si>
+    <t>E864,E1006,E612,E983,E1286,E1503,E451,E352,E1431,E1191,E738,E138,E2642,E2274,E2433,E139,E863,E1115,E140,E717,E1226,E1507,E249,E1203,E1423,E1838,E1045,E1782,E527,E707,E256,E859,E1839,E719,E1117,E432,E667,E1107,E447,E433,E1206,E721,E1207,E1517,E1770,E248,E2440,E723,E461,E136</t>
+  </si>
+  <si>
+    <t>C00079/CE2172,C06199,C00355,C06350,CE6316,C05584,CE2176,tymsf,C00588/C05594,C05577/C00544/C01161,CE5627,C05589/C00788,C15522/thbpt4acam,C00020/C00362,C04043/C00642/C05852,C05589/C00788,C00079/CE2172,C05583/C05582,C05589/C00788,C05588,C02442/C03711,CE5536/C01586,CE5541/C13747/C07480,C09642,C05581,CE5538/C05653,CE1918/CE5629,C00822/C05604,C16586/CE2173,C13690,C00082/CE2174,C00079/CE2172,CE5538/C05653,C05588,C05583/C05582,C05587/C07453,C05580,C05838/C00811/C02763/C00166,CE2176,C05587/C07453,C09642,C05588,C09642,C05350/C01197/C01179,C00547/C00314,CE5541/C13747/C07480,C05576,C05588,CE5626,C05589/C00788</t>
+  </si>
+  <si>
+    <t>L-Phenylalanine/$Hordenine; 4-[2-(Dimethylamino)ethyl]phenol$3,4-Dihydroxy-L-phenylalanine$$N,N-dimethyldopaminequinone$3-Methoxy-4-hydroxymandelate; Vanillylmandelic acid$3-O-methyldopa$Tyramine O-sulfate$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$3,4-Dihydroxymandelaldehyde/Homogentisate/3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$salsoline-1-carboxylate$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$AMP/dGMP$3,4-Dihydroxyphenylacetaldehyde; Protocatechuatealdehyde/4-Hydroxyphenylacetate/2-Hydroxyphenylacetate$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Phenylalanine/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Metanephrine$N-Methyltyramine/N-Methylphenylethanolamine$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$adrenochrome o-semiquinone/1,7-Dimethylxanthine; Paraxanthine/$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$3-Methoxy-4-hydroxyphenylacetaldehyde$noradrenochrome/N-Formylanthranilate$5-hydroxytryptophol/1,2-dehydrosalsolinol$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$2-Phenyl-1,3-propanediol monocarbamate/$Dopamine 3-O-sulfate$L-Tyrosine/$L-Phenylalanine/$noradrenochrome/N-Formylanthranilate$L-Metanephrine$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$3-Methoxytyramine/Epinine; Deoxyepinephrine$3,4-Dihydroxymandelate$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$3-O-methyldopa$3-Methoxytyramine/Epinine; Deoxyepinephrine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$L-Metanephrine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$2-Hydroxy-3-(4-hydroxyphenyl)propenoate; 4-Hydroxy-enol-phenylpyruvate/Caffeate; Caffeic acid; 3,4-Dihydroxy-trans-cinnamate; trans-Caffeate/3-(4-Hydroxyphenyl)pyruvate$Norepinephrine/Pyridoxine$adrenochrome o-semiquinone/1,7-Dimethylxanthine; Paraxanthine/$3,4-Dihydroxyphenylethyleneglycol$L-Metanephrine$salsolinol 1-carboxylate$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol</t>
   </si>
   <si>
     <t>Glycerophospholipid metabolism</t>
   </si>
   <si>
-    <t>E238,E317,E628,E1483,E239,E1340,E1432,E653,E2088,E318,E1339,E237,E351,E681,E319</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C06426/C06427,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,C06124,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00670,C00588/C05594,C00836,C00219,C15646,C00670,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00055,C01194,C15646</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$Sphingosine 1-phosphate$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$sn-Glycero-3-phosphocholine$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$Sphinganine$arachidonic acid$1-(1-Alkenyl)-sn-glycero-3-phosphate$sn-Glycero-3-phosphocholine$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$CMP$Phosphatidylinositol$1-(1-Alkenyl)-sn-glycero-3-phosphate</t>
-  </si>
-  <si>
-    <t>Tyrosine metabolism</t>
-  </si>
-  <si>
-    <t>E259,E1501,E1208,E249,E1111,E1518,E864,E462,E1773,E250,E1821,E1007,E613,E138,E984,E1287,E1504,E1785,E452,E252,E139,E353,E1432,E1192,E739,E615,E430,E1116,E718,E1227,E1424,E1508,E1204,E1839,E667,E1046,E528,E708,E257,E860,E720,E1118,E1510,E608,E433,E1108,E668,E1516,E1473,E258,E448,E1048,E434,E1207,E2193,E722,E610,E1110,E136</t>
-  </si>
-  <si>
-    <t>C00082/CE2174,C05584,C09642,CE5541/C13747/C07480,C05838/C00811/C02763/C00166,C05350/C01197/C01179,C00079/CE2172,CE5626,C00547/C00314,CE5541/C13747/C07480,CE5025,C06199,C00355,C05589/C00788,C06350,CE6316,C05584,C00822/C05604,CE2176,CE5541/C13747/C07480,C05589/C00788,tymsf,C00588/C05594,C05577/C00544/C01161,CE5627,C00355,C05587/C07453,C05583/C05582,C05588,C02442/C03711,C05581,CE5536/C01586,C09642,CE5538/C05653,C05580,CE1918/CE5629,C16586/CE2173,C13690,C00082/CE2174,C00079/CE2172,C05588,C05583/C05582,CE5536/C01586,C03758,C05587/C07453,C05838/C00811/C02763/C00166,C05580,C05350/C01197/C01179,C00268/C02953/C04244,C00082/CE2174,CE2176,CE1918/CE5629,C05587/C07453,C09642,CE5277,C05588,C03758,C05838/C00811/C02763/C00166,C05589/C00788</t>
-  </si>
-  <si>
-    <t>L-Tyrosine/$3-Methoxy-4-hydroxymandelate; Vanillylmandelic acid$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$adrenochrome o-semiquinone/1,7-Dimethylxanthine; Paraxanthine/$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$2-Hydroxy-3-(4-hydroxyphenyl)propenoate; 4-Hydroxy-enol-phenylpyruvate/Caffeate; Caffeic acid; 3,4-Dihydroxy-trans-cinnamate; trans-Caffeate/3-(4-Hydroxyphenyl)pyruvate$L-Phenylalanine/$salsolinol 1-carboxylate$Norepinephrine/Pyridoxine$adrenochrome o-semiquinone/1,7-Dimethylxanthine; Paraxanthine/$5-S-glutathionyl-dopamine$Hordenine; 4-[2-(Dimethylamino)ethyl]phenol$3,4-Dihydroxy-L-phenylalanine$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$N,N-dimethyldopaminequinone$3-Methoxy-4-hydroxymandelate; Vanillylmandelic acid$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$3-O-methyldopa$adrenochrome o-semiquinone/1,7-Dimethylxanthine; Paraxanthine/$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$Tyramine O-sulfate$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$3,4-Dihydroxymandelaldehyde/Homogentisate/3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$salsoline-1-carboxylate$3,4-Dihydroxy-L-phenylalanine$3-Methoxytyramine/Epinine; Deoxyepinephrine$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$L-Metanephrine$N-Methyltyramine/N-Methylphenylethanolamine$3-Methoxy-4-hydroxyphenylacetaldehyde$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$noradrenochrome/N-Formylanthranilate$3,4-Dihydroxymandelate$5-hydroxytryptophol/1,2-dehydrosalsolinol$2-Phenyl-1,3-propanediol monocarbamate/$Dopamine 3-O-sulfate$L-Tyrosine/$L-Phenylalanine/$L-Metanephrine$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$Dopamine$3-Methoxytyramine/Epinine; Deoxyepinephrine$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$3,4-Dihydroxymandelate$2-Hydroxy-3-(4-hydroxyphenyl)propenoate; 4-Hydroxy-enol-phenylpyruvate/Caffeate; Caffeic acid; 3,4-Dihydroxy-trans-cinnamate; trans-Caffeate/3-(4-Hydroxyphenyl)pyruvate$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$L-Tyrosine/$3-O-methyldopa$5-hydroxytryptophol/1,2-dehydrosalsolinol$3-Methoxytyramine/Epinine; Deoxyepinephrine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$aminochrome o-semiquinone$L-Metanephrine$Dopamine$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol</t>
+    <t>E350,E652,E680,E1339,E237,E316,E627,E1482,E1431,E2087,E317,E236</t>
+  </si>
+  <si>
+    <t>C00055,C00836,C01194,C00670,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C06426/C06427,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,C06124,C00588/C05594,C00219,C15646,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159</t>
+  </si>
+  <si>
+    <t>CMP$Sphinganine$Phosphatidylinositol$sn-Glycero-3-phosphocholine$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$Sphingosine 1-phosphate$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$arachidonic acid$1-(1-Alkenyl)-sn-glycero-3-phosphate$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose</t>
+  </si>
+  <si>
+    <t>De novo fatty acid biosynthesis</t>
+  </si>
+  <si>
+    <t>E1436,E2274,E316,E2087,E2093</t>
+  </si>
+  <si>
+    <t>C00249,C00020/C00362,C06426/C06427,C00219,C00712</t>
+  </si>
+  <si>
+    <t>Hexadecanoate (n-C16:0)$AMP/dGMP$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$arachidonic acid$(9Z)-Octadecenoic acid; (Z)-Octadec-9-enoic acid; Oleate; Oleic acid</t>
+  </si>
+  <si>
+    <t>CoA Catabolism</t>
+  </si>
+  <si>
+    <t>E14,E15,E297,E2274</t>
+  </si>
+  <si>
+    <t>C00831,C00831,C00864,C00020/C00362</t>
+  </si>
+  <si>
+    <t>Pantetheine; (R)-Pantetheine$Pantetheine; (R)-Pantetheine$(R)-Pantothenate$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Pyrimidine metabolism</t>
+  </si>
+  <si>
+    <t>E350,E598,E2274,E581,E1716,E582,E2510</t>
+  </si>
+  <si>
+    <t>C00055,C00214,C00020/C00362,C00526,C05711/C00475,C00526,C00399</t>
+  </si>
+  <si>
+    <t>CMP$Thymidine$AMP/dGMP$Deoxyuridine$gamma-Glutamyl-beta-cyanoalanine/Cytidine$Deoxyuridine$Ubiquinone</t>
+  </si>
+  <si>
+    <t>Omega-3 fatty acid metabolism</t>
+  </si>
+  <si>
+    <t>E51,E316,E2274</t>
+  </si>
+  <si>
+    <t>C16300,C06426/C06427,C00020/C00362</t>
+  </si>
+  <si>
+    <t>Stearidonic acid; 6,9,12,15-Octadecatetraenoic acid; (6Z,9Z,12Z,15Z)-Octadecatetraenoic acid$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Omega-6 fatty acid metabolism</t>
+  </si>
+  <si>
+    <t>E2087,E2274</t>
+  </si>
+  <si>
+    <t>C00219,C00020/C00362</t>
+  </si>
+  <si>
+    <t>arachidonic acid$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Leukotriene metabolism</t>
+  </si>
+  <si>
+    <t>E16,E1367,E2274,E18,E170,E1393,E1589,E1259,E805,E1357,E837,E2087,E2073,E1260</t>
+  </si>
+  <si>
+    <t>,,C00020/C00362,,,,,,,,,C00219,,</t>
+  </si>
+  <si>
+    <t>$$AMP/dGMP$$$$$$$$$arachidonic acid$$</t>
   </si>
   <si>
     <t>Biopterin metabolism</t>
   </si>
   <si>
-    <t>E257,E259,E860,E521,E258,E864,E519,E522,E1473,E1482</t>
-  </si>
-  <si>
-    <t>C00082/CE2174,C00082/CE2174,C00079/CE2172,CE2705/CE5236,C00082/CE2174,C00079/CE2172,CE2705/CE5236,CE2705/CE5236,C00268/C02953/C04244,C03684/C00835</t>
-  </si>
-  <si>
-    <t>L-Tyrosine/$L-Tyrosine/$L-Phenylalanine/$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$L-Tyrosine/$L-Phenylalanine/$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$6-Pyruvoyl-5,6,7,8-tetrahydropterin/Sepiapterin</t>
+    <t>E2642,E864,E256,E859,E520,E863,E518</t>
+  </si>
+  <si>
+    <t>C15522/thbpt4acam,C00079/CE2172,C00082/CE2174,C00079/CE2172,,C00079/CE2172,</t>
+  </si>
+  <si>
+    <t>Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$L-Phenylalanine/$L-Tyrosine/$L-Phenylalanine/$$L-Phenylalanine/$</t>
   </si>
   <si>
     <t>Glycosphingolipid biosynthesis - globoseries</t>
   </si>
   <si>
-    <t>E238,E351,E239,E237</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00055,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$CMP$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose</t>
-  </si>
-  <si>
-    <t>CoA Catabolism</t>
-  </si>
-  <si>
-    <t>E298,E15,E304,E14</t>
-  </si>
-  <si>
-    <t>C00864,C00831,C00864,C00831</t>
-  </si>
-  <si>
-    <t>(R)-Pantothenate$Pantetheine; (R)-Pantetheine$(R)-Pantothenate$Pantetheine; (R)-Pantetheine</t>
+    <t>E350,E237,E236</t>
+  </si>
+  <si>
+    <t>C00055,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159</t>
+  </si>
+  <si>
+    <t>CMP$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose</t>
+  </si>
+  <si>
+    <t>Fatty acid activation</t>
+  </si>
+  <si>
+    <t>E1436,E316,E2274</t>
+  </si>
+  <si>
+    <t>C00249,C06426/C06427,C00020/C00362</t>
+  </si>
+  <si>
+    <t>Hexadecanoate (n-C16:0)$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Fatty Acid Metabolism</t>
+  </si>
+  <si>
+    <t>E981,E1436</t>
+  </si>
+  <si>
+    <t>,C00249</t>
+  </si>
+  <si>
+    <t>$Hexadecanoate (n-C16:0)</t>
+  </si>
+  <si>
+    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
+  </si>
+  <si>
+    <t>Butanoate metabolism</t>
+  </si>
+  <si>
+    <t>E849,E1760,E848,E2274</t>
+  </si>
+  <si>
+    <t>,,,C00020/C00362</t>
+  </si>
+  <si>
+    <t>$$$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Saturated fatty acids beta-oxidation</t>
+  </si>
+  <si>
+    <t>E1436</t>
+  </si>
+  <si>
+    <t>C00249</t>
+  </si>
+  <si>
+    <t>Hexadecanoate (n-C16:0)</t>
+  </si>
+  <si>
+    <t>Keratan sulfate biosynthesis</t>
+  </si>
+  <si>
+    <t>E350</t>
+  </si>
+  <si>
+    <t>C00055</t>
+  </si>
+  <si>
+    <t>CMP</t>
+  </si>
+  <si>
+    <t>O-Glycan biosynthesis</t>
+  </si>
+  <si>
+    <t>Bile acid biosynthesis</t>
+  </si>
+  <si>
+    <t>E329,E2274,E1629,E327,E783,E789,E331</t>
+  </si>
+  <si>
+    <t>,C00020/C00362,,,,,</t>
+  </si>
+  <si>
+    <t>$AMP/dGMP$$$$$</t>
+  </si>
+  <si>
+    <t>Vitamin B2 (riboflavin) metabolism</t>
+  </si>
+  <si>
+    <t>E439,E883,E2274</t>
+  </si>
+  <si>
+    <t>,,C00020/C00362</t>
+  </si>
+  <si>
+    <t>$$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Propanoate metabolism</t>
+  </si>
+  <si>
+    <t>E2047,E2274</t>
+  </si>
+  <si>
+    <t>,C00020/C00362</t>
+  </si>
+  <si>
+    <t>$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Sialic acid metabolism</t>
+  </si>
+  <si>
+    <t>E350,E680,E237,E813,E236</t>
+  </si>
+  <si>
+    <t>C00055,C01194,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159</t>
+  </si>
+  <si>
+    <t>CMP$Phosphatidylinositol$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose</t>
+  </si>
+  <si>
+    <t>Pentose phosphate pathway</t>
+  </si>
+  <si>
+    <t>E236,E237,E1724,E2274</t>
+  </si>
+  <si>
+    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,,C00020/C00362</t>
+  </si>
+  <si>
+    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Lysine metabolism</t>
+  </si>
+  <si>
+    <t>E1941,E1012,E741,E2274</t>
+  </si>
+  <si>
+    <t>Linoleate metabolism</t>
+  </si>
+  <si>
+    <t>E975,E1182,E316,E973,E857,E1240,E64,E1377,E858,E558,E45,E1241</t>
+  </si>
+  <si>
+    <t>,,C06426/C06427,,,,,,,,,</t>
+  </si>
+  <si>
+    <t>$$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$$$$$$$$$</t>
+  </si>
+  <si>
+    <t>Urea cycle/amino group metabolism</t>
+  </si>
+  <si>
+    <t>E138,E570,E1770,E139,E563,E1226,E2197,E140,E564,E1941,E1507,E136</t>
+  </si>
+  <si>
+    <t>C05589/C00788,,C00547/C00314,C05589/C00788,,C02442/C03711,,C05589/C00788,,,CE5536/C01586,C05589/C00788</t>
+  </si>
+  <si>
+    <t>L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$Norepinephrine/Pyridoxine$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$N-Methyltyramine/N-Methylphenylethanolamine$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol</t>
+  </si>
+  <si>
+    <t>Arachidonic acid metabolism</t>
+  </si>
+  <si>
+    <t>E1367,E2274,E170,E316,E627,E1354,E2087</t>
+  </si>
+  <si>
+    <t>,C00020/C00362,,C06426/C06427,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,,C00219</t>
+  </si>
+  <si>
+    <t>$AMP/dGMP$$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$$arachidonic acid</t>
+  </si>
+  <si>
+    <t>Porphyrin metabolism</t>
+  </si>
+  <si>
+    <t>E402,E405,E512,E1971</t>
+  </si>
+  <si>
+    <t>,,,</t>
+  </si>
+  <si>
+    <t>$$$</t>
+  </si>
+  <si>
+    <t>Mono-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>E2274</t>
+  </si>
+  <si>
+    <t>C00020/C00362</t>
+  </si>
+  <si>
+    <t>AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Phytanic acid peroxisomal oxidation</t>
+  </si>
+  <si>
+    <t>D4&amp;E4-neuroprostanes formation</t>
+  </si>
+  <si>
+    <t>E134,E2182,E358</t>
+  </si>
+  <si>
+    <t>,,</t>
+  </si>
+  <si>
+    <t>$$</t>
+  </si>
+  <si>
+    <t>Starch and Sucrose Metabolism</t>
+  </si>
+  <si>
+    <t>E237,E236</t>
+  </si>
+  <si>
+    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159</t>
+  </si>
+  <si>
+    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose</t>
+  </si>
+  <si>
+    <t>Aspartate and asparagine metabolism</t>
+  </si>
+  <si>
+    <t>E223,E2274,E505,E1941,E1454</t>
+  </si>
+  <si>
+    <t>,C00020/C00362,,,</t>
+  </si>
+  <si>
+    <t>$AMP/dGMP$$$</t>
+  </si>
+  <si>
+    <t>Histidine metabolism</t>
+  </si>
+  <si>
+    <t>E1631,E1636,E802,E2274</t>
+  </si>
+  <si>
+    <t>Vitamin B6 (pyridoxine) metabolism</t>
+  </si>
+  <si>
+    <t>E1770,E1845,E1185,E1846</t>
+  </si>
+  <si>
+    <t>C00547/C00314,,,</t>
+  </si>
+  <si>
+    <t>Norepinephrine/Pyridoxine$$$</t>
+  </si>
+  <si>
+    <t>Glycolysis and Gluconeogenesis</t>
+  </si>
+  <si>
+    <t>E237,E236,E2274</t>
+  </si>
+  <si>
+    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00020/C00362</t>
+  </si>
+  <si>
+    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Vitamin D3 (cholecalciferol) metabolism</t>
+  </si>
+  <si>
+    <t>E30,E783</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>$</t>
+  </si>
+  <si>
+    <t>Vitamin B1 (thiamin) metabolism</t>
+  </si>
+  <si>
+    <t>E741,E2274</t>
+  </si>
+  <si>
+    <t>Vitamin E metabolism</t>
+  </si>
+  <si>
+    <t>E2274,E1487</t>
+  </si>
+  <si>
+    <t>C00020/C00362,</t>
+  </si>
+  <si>
+    <t>AMP/dGMP$</t>
+  </si>
+  <si>
+    <t>Beta-Alanine metabolism</t>
+  </si>
+  <si>
+    <t>E1631,E1636</t>
+  </si>
+  <si>
+    <t>N-Glycan biosynthesis</t>
   </si>
   <si>
     <t>Hexose phosphorylation</t>
   </si>
   <si>
-    <t>E238,E1108,E1111,E239,E2058,E928,E237,E929,E1110</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C05838/C00811/C02763/C00166,C05838/C00811/C02763/C00166,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00329,C05839,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C05839,C05838/C00811/C02763/C00166</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$D-Glucosamine$cis-beta-D-Glucosyl-2-hydroxycinnamate; beta-D-Glucosyl-2-coumarinate$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$cis-beta-D-Glucosyl-2-hydroxycinnamate; beta-D-Glucosyl-2-coumarinate$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate</t>
-  </si>
-  <si>
-    <t>Pentose phosphate pathway</t>
-  </si>
-  <si>
-    <t>E238,E239,E1725,E2196,E237,E1987</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,,,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$$$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$</t>
-  </si>
-  <si>
-    <t>Vitamin B2 (riboflavin) metabolism</t>
-  </si>
-  <si>
-    <t>E440,E900,E884,E882</t>
-  </si>
-  <si>
-    <t>,,,</t>
-  </si>
-  <si>
-    <t>$$$</t>
-  </si>
-  <si>
-    <t>Sialic acid metabolism</t>
-  </si>
-  <si>
-    <t>E238,E1468,E814,E239,E237,E351,E681</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,,,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00055,C01194</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$$$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$CMP$Phosphatidylinositol</t>
-  </si>
-  <si>
-    <t>Starch and Sucrose Metabolism</t>
-  </si>
-  <si>
-    <t>E238,E239,E237</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose</t>
-  </si>
-  <si>
-    <t>De novo fatty acid biosynthesis</t>
-  </si>
-  <si>
-    <t>E317,E2088,E1437,E2094</t>
-  </si>
-  <si>
-    <t>C06426/C06427,C00219,C00249,</t>
-  </si>
-  <si>
-    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$arachidonic acid$Hexadecanoate (n-C16:0)$</t>
-  </si>
-  <si>
-    <t>N-Glycan biosynthesis</t>
-  </si>
-  <si>
-    <t>E238,E2230,E239,E237,E351</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00055</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$CMP</t>
+    <t>E928,E237,E1107,E927,E236</t>
+  </si>
+  <si>
+    <t>,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C05838/C00811/C02763/C00166,,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159</t>
+  </si>
+  <si>
+    <t>$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - lactoseries</t>
+  </si>
+  <si>
+    <t>Blood Group Biosynthesis</t>
+  </si>
+  <si>
+    <t>Electron transport chain</t>
+  </si>
+  <si>
+    <t>E2510</t>
+  </si>
+  <si>
+    <t>C00399</t>
+  </si>
+  <si>
+    <t>Ubiquinone</t>
+  </si>
+  <si>
+    <t>Fatty acid oxidation</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - neolactoseries</t>
+  </si>
+  <si>
+    <t>Glutathione Metabolism</t>
+  </si>
+  <si>
+    <t>E1454</t>
+  </si>
+  <si>
+    <t>Prostaglandin formation from dihomo gama-linoleic acid</t>
+  </si>
+  <si>
+    <t>E1357</t>
+  </si>
+  <si>
+    <t>Carnitine shuttle</t>
+  </si>
+  <si>
+    <t>E1173,E956,E224,E957,E228,E192</t>
+  </si>
+  <si>
+    <t>,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$</t>
+  </si>
+  <si>
+    <t>Alkaloid biosynthesis II</t>
+  </si>
+  <si>
+    <t>E1273,E2274</t>
+  </si>
+  <si>
+    <t>C21-steroid hormone biosynthesis and metabolism</t>
+  </si>
+  <si>
+    <t>E208,E157,E310,E148,E1676,E39,E119,E73,E109,E415,E1674,E85,E306,E129</t>
+  </si>
+  <si>
+    <t>,,,,,,,,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$$$$$$$</t>
+  </si>
+  <si>
+    <t>Limonene and pinene degradation</t>
+  </si>
+  <si>
+    <t>E1317,E1555,E1558</t>
+  </si>
+  <si>
+    <t>Fructose and mannose metabolism</t>
+  </si>
+  <si>
+    <t>E427,E237,E2174,E236</t>
+  </si>
+  <si>
+    <t>,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159</t>
+  </si>
+  <si>
+    <t>$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose</t>
+  </si>
+  <si>
+    <t>Glycine, serine, alanine and threonine metabolism</t>
+  </si>
+  <si>
+    <t>E969,E263,E2274,E2197,E262</t>
+  </si>
+  <si>
+    <t>,,C00020/C00362,,</t>
+  </si>
+  <si>
+    <t>$$AMP/dGMP$$</t>
+  </si>
+  <si>
+    <t>Di-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>Valine, leucine and isoleucine degradation</t>
+  </si>
+  <si>
+    <t>Pentose and Glucuronate Interconversions</t>
+  </si>
+  <si>
+    <t>E1724</t>
+  </si>
+  <si>
+    <t>Selenoamino acid metabolism</t>
+  </si>
+  <si>
+    <t>Vitamin A (retinol) metabolism</t>
+  </si>
+  <si>
+    <t>E180,E163,E627,E2274</t>
+  </si>
+  <si>
+    <t>,,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,C00020/C00362</t>
+  </si>
+  <si>
+    <t>$$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Ubiquinone Biosynthesis</t>
+  </si>
+  <si>
+    <t>E1517,E1107,E2510,E2274</t>
+  </si>
+  <si>
+    <t>C05350/C01197/C01179,C05838/C00811/C02763/C00166,C00399,C00020/C00362</t>
+  </si>
+  <si>
+    <t>2-Hydroxy-3-(4-hydroxyphenyl)propenoate; 4-Hydroxy-enol-phenylpyruvate/Caffeate; Caffeic acid; 3,4-Dihydroxy-trans-cinnamate; trans-Caffeate/3-(4-Hydroxyphenyl)pyruvate$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$Ubiquinone$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Caffeine metabolism</t>
+  </si>
+  <si>
+    <t>E248,E249</t>
+  </si>
+  <si>
+    <t>CE5541/C13747/C07480,CE5541/C13747/C07480</t>
+  </si>
+  <si>
+    <t>adrenochrome o-semiquinone/1,7-Dimethylxanthine; Paraxanthine/$adrenochrome o-semiquinone/1,7-Dimethylxanthine; Paraxanthine/</t>
+  </si>
+  <si>
+    <t>Prostaglandin formation from arachidonate</t>
+  </si>
+  <si>
+    <t>E1042,E369,E912,E1367,E2274,E1357,E2087</t>
+  </si>
+  <si>
+    <t>,,,,C00020/C00362,,C00219</t>
+  </si>
+  <si>
+    <t>$$$$AMP/dGMP$$arachidonic acid</t>
+  </si>
+  <si>
+    <t>Vitamin H (biotin) metabolism</t>
+  </si>
+  <si>
+    <t>Drug metabolism - cytochrome P450</t>
+  </si>
+  <si>
+    <t>E527,E187,E477,E699,E472,E475,E1889,E964</t>
+  </si>
+  <si>
+    <t>C16586/CE2173,C16591,,C16609,,,C16608,C16595/C16587</t>
+  </si>
+  <si>
+    <t>2-Phenyl-1,3-propanediol monocarbamate/$3-Carbamoyl-2-phenylpropionic acid$$Didemethylcitalopram$$$Demethylcitalopram$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one/3-Carbamoyl-2-phenylpropionaldehyde</t>
+  </si>
+  <si>
+    <t>Vitamin B9 (folate) metabolism</t>
+  </si>
+  <si>
+    <t>E1947,E540</t>
+  </si>
+  <si>
+    <t>Arginine and Proline Metabolism</t>
+  </si>
+  <si>
+    <t>E1941,E2197</t>
+  </si>
+  <si>
+    <t>Lipoate metabolism</t>
+  </si>
+  <si>
+    <t>E2047</t>
+  </si>
+  <si>
+    <t>N-Glycan Degradation</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - ganglioseries</t>
+  </si>
+  <si>
+    <t>Alanine and Aspartate Metabolism</t>
+  </si>
+  <si>
+    <t>Ascorbate (Vitamin C) and Aldarate Metabolism</t>
+  </si>
+  <si>
+    <t>E2047,E266,E1724</t>
+  </si>
+  <si>
+    <t>Putative anti-Inflammatory metabolites formation from EPA</t>
+  </si>
+  <si>
+    <t>E1367</t>
+  </si>
+  <si>
+    <t>Squalene and cholesterol biosynthesis</t>
+  </si>
+  <si>
+    <t>E2311</t>
+  </si>
+  <si>
+    <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
+  </si>
+  <si>
+    <t>Galactose metabolism</t>
+  </si>
+  <si>
+    <t>TCA cycle</t>
+  </si>
+  <si>
+    <t>Androgen and estrogen biosynthesis and metabolism</t>
+  </si>
+  <si>
+    <t>E157,E148,E1676,E39,E415,E1674,E85,E129</t>
+  </si>
+  <si>
+    <t>,,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$</t>
+  </si>
+  <si>
+    <t>Methionine and cysteine metabolism</t>
+  </si>
+  <si>
+    <t>E2197,E2274</t>
+  </si>
+  <si>
+    <t>Aminosugars metabolism</t>
+  </si>
+  <si>
+    <t>Xenobiotics metabolism</t>
+  </si>
+  <si>
+    <t>Tryptophan metabolism</t>
+  </si>
+  <si>
+    <t>E589,E395,E75,E340,E10,E1223,E643,E507,E2642,E2026,E2274,E1726,E78,E944,E1214,E987,E1838,E1045,E946,E1839,E1850</t>
+  </si>
+  <si>
+    <t>C05638,,,,,,,,C15522/thbpt4acam,,C00020/C00362,,,,,,CE5538/C05653,CE1918/CE5629,,CE5538/C05653,</t>
+  </si>
+  <si>
+    <t>5-Hydroxykynurenamine$$$$$$$$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$$AMP/dGMP$$$$$$noradrenochrome/N-Formylanthranilate$5-hydroxytryptophol/1,2-dehydrosalsolinol$$noradrenochrome/N-Formylanthranilate$</t>
+  </si>
+  <si>
+    <t>Purine metabolism</t>
+  </si>
+  <si>
+    <t>E239,E1734,E246,E2274</t>
+  </si>
+  <si>
+    <t>Hyaluronan Metabolism</t>
+  </si>
+  <si>
+    <t>R Group Synthesis</t>
+  </si>
+  <si>
+    <t>C5-Branched dibasic acid metabolism</t>
+  </si>
+  <si>
+    <t>Pyruvate Metabolism</t>
+  </si>
+  <si>
+    <t>Chondroitin sulfate degradation</t>
+  </si>
+  <si>
+    <t>Keratan sulfate degradation</t>
+  </si>
+  <si>
+    <t>Glycerolipid metabolism</t>
+  </si>
+  <si>
+    <t>3-oxo-10R-octadecatrienoate beta-oxidation</t>
+  </si>
+  <si>
+    <t>Glycosylphosphatidylinositol(GPI)-anchor biosynthesis</t>
+  </si>
+  <si>
+    <t>Parathio degradation</t>
+  </si>
+  <si>
+    <t>Heparan sulfate biosynthesis</t>
   </si>
   <si>
     <t>Glyoxylate and Dicarboxylate Metabolism</t>
   </si>
   <si>
-    <t>E2196</t>
-  </si>
-  <si>
-    <t>Saturated fatty acids beta-oxidation</t>
-  </si>
-  <si>
-    <t>E1437</t>
-  </si>
-  <si>
-    <t>C00249</t>
-  </si>
-  <si>
-    <t>Hexadecanoate (n-C16:0)</t>
-  </si>
-  <si>
-    <t>Keratan sulfate biosynthesis</t>
-  </si>
-  <si>
-    <t>E351</t>
-  </si>
-  <si>
-    <t>C00055</t>
-  </si>
-  <si>
-    <t>CMP</t>
-  </si>
-  <si>
-    <t>O-Glycan biosynthesis</t>
-  </si>
-  <si>
-    <t>Fatty acid activation</t>
-  </si>
-  <si>
-    <t>E317,E1437,E1810</t>
-  </si>
-  <si>
-    <t>C06426/C06427,C00249,</t>
-  </si>
-  <si>
-    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$Hexadecanoate (n-C16:0)$</t>
-  </si>
-  <si>
-    <t>Beta-Alanine metabolism</t>
-  </si>
-  <si>
-    <t>E1383,E1637,E1632</t>
-  </si>
-  <si>
-    <t>,,</t>
-  </si>
-  <si>
-    <t>$$</t>
-  </si>
-  <si>
-    <t>Fatty Acid Metabolism</t>
-  </si>
-  <si>
-    <t>E1437,E982</t>
-  </si>
-  <si>
-    <t>C00249,</t>
-  </si>
-  <si>
-    <t>Hexadecanoate (n-C16:0)$</t>
-  </si>
-  <si>
-    <t>Pentose and Glucuronate Interconversions</t>
-  </si>
-  <si>
-    <t>E2196,E1725</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
-    <t>C21-steroid hormone biosynthesis and metabolism</t>
-  </si>
-  <si>
-    <t>E1145,E368,E148,E1873,E369,E129,E416,E119,E109,E157,E1676,E1940,E209,E870,E307,E39,E73,E85,E1306,E311</t>
-  </si>
-  <si>
-    <t>,,,,,,,,,,,,,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$$$$$$$$$$$$</t>
-  </si>
-  <si>
-    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
-  </si>
-  <si>
-    <t>E298,E304,E14,E15</t>
-  </si>
-  <si>
-    <t>C00864,C00864,C00831,C00831</t>
-  </si>
-  <si>
-    <t>(R)-Pantothenate$(R)-Pantothenate$Pantetheine; (R)-Pantetheine$Pantetheine; (R)-Pantetheine</t>
-  </si>
-  <si>
-    <t>Fructose and mannose metabolism</t>
-  </si>
-  <si>
-    <t>E238,E239,E428,E2175,E237,E1479</t>
-  </si>
-  <si>
-    <t>Omega-3 fatty acid metabolism</t>
-  </si>
-  <si>
-    <t>E51,E317</t>
-  </si>
-  <si>
-    <t>,C06426/C06427</t>
-  </si>
-  <si>
-    <t>$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate</t>
-  </si>
-  <si>
-    <t>Urea cycle/amino group metabolism</t>
-  </si>
-  <si>
-    <t>E138,E1510,E1383,E1950,E1805,E139,E565,E1227,E1508,E1942,E1773,E571,E1083,E136</t>
-  </si>
-  <si>
-    <t>C05589/C00788,CE5536/C01586,,,,C05589/C00788,,C02442/C03711,CE5536/C01586,,C00547/C00314,,,C05589/C00788</t>
-  </si>
-  <si>
-    <t>L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$$$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$N-Methyltyramine/N-Methylphenylethanolamine$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$$Norepinephrine/Pyridoxine$$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol</t>
-  </si>
-  <si>
-    <t>N-Glycan Degradation</t>
-  </si>
-  <si>
-    <t>E238,E1468,E239,E237</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose</t>
-  </si>
-  <si>
-    <t>Chondroitin sulfate degradation</t>
-  </si>
-  <si>
-    <t>Bile acid biosynthesis</t>
-  </si>
-  <si>
-    <t>E1630,E328,E784,E790,E332,E1629,E330</t>
-  </si>
-  <si>
-    <t>,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$</t>
-  </si>
-  <si>
-    <t>Drug metabolism - cytochrome P450</t>
-  </si>
-  <si>
-    <t>E478,E187,E700,E495,E473,E476,E185,E1890,E1302,E965,E528,E188</t>
-  </si>
-  <si>
-    <t>,C16591,C16609,,,,C16591,C16608,C07572,C16595/C16587,C16586/CE2173,C16591</t>
-  </si>
-  <si>
-    <t>$3-Carbamoyl-2-phenylpropionic acid$Didemethylcitalopram$$$$3-Carbamoyl-2-phenylpropionic acid$Demethylcitalopram$Citalopram$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one/3-Carbamoyl-2-phenylpropionaldehyde$2-Phenyl-1,3-propanediol monocarbamate/$3-Carbamoyl-2-phenylpropionic acid</t>
+    <t>Glycosaminoglycan degradation</t>
+  </si>
+  <si>
+    <t>ROS Detoxification</t>
+  </si>
+  <si>
+    <t>Geraniol degradation</t>
+  </si>
+  <si>
+    <t>Vitamin D</t>
+  </si>
+  <si>
+    <t>Dynorphin metabolism</t>
+  </si>
+  <si>
+    <t>Heparan sulfate degradation</t>
+  </si>
+  <si>
+    <t>Fatty acid oxidation, peroxisome</t>
+  </si>
+  <si>
+    <t>Polyunsaturated fatty acid biosynthesis</t>
+  </si>
+  <si>
+    <t>3-Chloroacrylic acid degradation</t>
+  </si>
+  <si>
+    <t>Sphingolipid metabolism</t>
+  </si>
+  <si>
+    <t>Proteoglycan biosynthesis</t>
+  </si>
+  <si>
+    <t>Vitamin K metabolism</t>
+  </si>
+  <si>
+    <t>Glutamate metabolism</t>
+  </si>
+  <si>
+    <t>Benzoate degradation via CoA ligation</t>
+  </si>
+  <si>
+    <t>Dimethyl-branched-chain fatty acid mitochondrial beta-oxidation</t>
+  </si>
+  <si>
+    <t>Atrazine degradation</t>
+  </si>
+  <si>
+    <t>Vitamin B12 (cyanocobalamin) metabolism</t>
+  </si>
+  <si>
+    <t>Carbon fixation</t>
+  </si>
+  <si>
+    <t>Nucleotide Sugar Metabolism</t>
+  </si>
+  <si>
+    <t>1- and 2-Methylnaphthalene degradation</t>
+  </si>
+  <si>
+    <t>Nitrogen metabolism</t>
   </si>
   <si>
     <t>Drug metabolism - other enzymes</t>
   </si>
   <si>
-    <t>E550,E2122</t>
-  </si>
-  <si>
-    <t>Pyrimidine metabolism</t>
-  </si>
-  <si>
-    <t>E1717,E583,E351,E599,E582</t>
-  </si>
-  <si>
-    <t>,,C00055,,</t>
-  </si>
-  <si>
-    <t>$$CMP$$</t>
-  </si>
-  <si>
-    <t>Caffeine metabolism</t>
-  </si>
-  <si>
-    <t>E249,E252,E250</t>
-  </si>
-  <si>
-    <t>CE5541/C13747/C07480,CE5541/C13747/C07480,CE5541/C13747/C07480</t>
-  </si>
-  <si>
-    <t>adrenochrome o-semiquinone/1,7-Dimethylxanthine; Paraxanthine/$adrenochrome o-semiquinone/1,7-Dimethylxanthine; Paraxanthine/$adrenochrome o-semiquinone/1,7-Dimethylxanthine; Paraxanthine/</t>
-  </si>
-  <si>
-    <t>D4&amp;E4-neuroprostanes formation</t>
-  </si>
-  <si>
-    <t>E2183,E134,E359</t>
-  </si>
-  <si>
-    <t>Linoleate metabolism</t>
-  </si>
-  <si>
-    <t>E317,E974,E2131,E858,E1241,E1183,E1378,E859,E559,E41,E64,E976,E45</t>
-  </si>
-  <si>
-    <t>C06426/C06427,,,,,,,,,,,,</t>
-  </si>
-  <si>
-    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$$$$$$$$$$$$</t>
-  </si>
-  <si>
-    <t>Porphyrin metabolism</t>
-  </si>
-  <si>
-    <t>E403,E406,E513,E1972</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - lactoseries</t>
-  </si>
-  <si>
-    <t>Blood Group Biosynthesis</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - neolactoseries</t>
-  </si>
-  <si>
-    <t>Glutathione Metabolism</t>
-  </si>
-  <si>
-    <t>E1455</t>
-  </si>
-  <si>
-    <t>Prostaglandin formation from dihomo gama-linoleic acid</t>
-  </si>
-  <si>
-    <t>E1358</t>
-  </si>
-  <si>
-    <t>Omega-6 fatty acid metabolism</t>
-  </si>
-  <si>
-    <t>E2088</t>
-  </si>
-  <si>
-    <t>C00219</t>
-  </si>
-  <si>
-    <t>arachidonic acid</t>
-  </si>
-  <si>
-    <t>Vitamin D3 (cholecalciferol) metabolism</t>
-  </si>
-  <si>
-    <t>E784,E30</t>
-  </si>
-  <si>
-    <t>Hyaluronan Metabolism</t>
-  </si>
-  <si>
-    <t>E1468,E1608</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - ganglioseries</t>
-  </si>
-  <si>
-    <t>E351,E2096</t>
-  </si>
-  <si>
-    <t>C00055,</t>
-  </si>
-  <si>
-    <t>CMP$</t>
-  </si>
-  <si>
-    <t>Heparan sulfate degradation</t>
-  </si>
-  <si>
-    <t>E1468,E2196</t>
-  </si>
-  <si>
-    <t>Glycolysis and Gluconeogenesis</t>
-  </si>
-  <si>
-    <t>Vitamin B9 (folate) metabolism</t>
-  </si>
-  <si>
-    <t>E2159,E1948,E541</t>
-  </si>
-  <si>
-    <t>Butanoate metabolism</t>
-  </si>
-  <si>
-    <t>E851,E849,E850</t>
-  </si>
-  <si>
-    <t>Carnitine shuttle</t>
-  </si>
-  <si>
-    <t>E2109,E225,E958,E229,E193,E1174,E957</t>
-  </si>
-  <si>
-    <t>Leukotriene metabolism</t>
-  </si>
-  <si>
-    <t>E18,E1260,E17,E170,E806,E838,E2074,E1358,E1261,E2088,E1267,E1368,E16</t>
-  </si>
-  <si>
-    <t>,,,,,,,,,C00219,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$$arachidonic acid$$$</t>
-  </si>
-  <si>
-    <t>Vitamin B6 (pyridoxine) metabolism</t>
-  </si>
-  <si>
-    <t>E1186,E1788,E1773,E1846</t>
-  </si>
-  <si>
-    <t>,,C00547/C00314,</t>
-  </si>
-  <si>
-    <t>$$Norepinephrine/Pyridoxine$</t>
-  </si>
-  <si>
-    <t>Ubiquinone Biosynthesis</t>
-  </si>
-  <si>
-    <t>E1108,E1111,E1516,E1110,E1518</t>
-  </si>
-  <si>
-    <t>C05838/C00811/C02763/C00166,C05838/C00811/C02763/C00166,C05350/C01197/C01179,C05838/C00811/C02763/C00166,C05350/C01197/C01179</t>
-  </si>
-  <si>
-    <t>cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$2-Hydroxy-3-(4-hydroxyphenyl)propenoate; 4-Hydroxy-enol-phenylpyruvate/Caffeate; Caffeic acid; 3,4-Dihydroxy-trans-cinnamate; trans-Caffeate/3-(4-Hydroxyphenyl)pyruvate$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$2-Hydroxy-3-(4-hydroxyphenyl)propenoate; 4-Hydroxy-enol-phenylpyruvate/Caffeate; Caffeic acid; 3,4-Dihydroxy-trans-cinnamate; trans-Caffeate/3-(4-Hydroxyphenyl)pyruvate</t>
-  </si>
-  <si>
-    <t>Aspartate and asparagine metabolism</t>
-  </si>
-  <si>
-    <t>E506,E1383,E1942,E1455,E224</t>
-  </si>
-  <si>
-    <t>,,,,</t>
-  </si>
-  <si>
-    <t>$$$$</t>
-  </si>
-  <si>
-    <t>Aminosugars metabolism</t>
-  </si>
-  <si>
-    <t>E351,E1468,E2058</t>
-  </si>
-  <si>
-    <t>C00055,,C00329</t>
-  </si>
-  <si>
-    <t>CMP$$D-Glucosamine</t>
-  </si>
-  <si>
-    <t>Valine, leucine and isoleucine degradation</t>
-  </si>
-  <si>
-    <t>E660</t>
-  </si>
-  <si>
-    <t>Galactose metabolism</t>
-  </si>
-  <si>
-    <t>Limonene and pinene degradation</t>
-  </si>
-  <si>
-    <t>E1555,E1318,E1559</t>
-  </si>
-  <si>
-    <t>Lysine metabolism</t>
-  </si>
-  <si>
-    <t>E742,E1013,E1942</t>
-  </si>
-  <si>
-    <t>Putative anti-Inflammatory metabolites formation from EPA</t>
-  </si>
-  <si>
-    <t>E2147,E1368</t>
-  </si>
-  <si>
-    <t>Arachidonic acid metabolism</t>
-  </si>
-  <si>
-    <t>E317,E628,E1355,E170,E2088,E1368</t>
-  </si>
-  <si>
-    <t>C06426/C06427,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,,,C00219,</t>
-  </si>
-  <si>
-    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$$$arachidonic acid$</t>
-  </si>
-  <si>
-    <t>Vitamin A (retinol) metabolism</t>
-  </si>
-  <si>
-    <t>E180,E628,E163,E2036</t>
-  </si>
-  <si>
-    <t>,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,,</t>
-  </si>
-  <si>
-    <t>$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$$</t>
-  </si>
-  <si>
-    <t>Histidine metabolism</t>
-  </si>
-  <si>
-    <t>E803,E1637,E1632</t>
-  </si>
-  <si>
-    <t>Keratan sulfate degradation</t>
-  </si>
-  <si>
-    <t>E1468</t>
-  </si>
-  <si>
-    <t>Lipoate metabolism</t>
-  </si>
-  <si>
-    <t>E1292</t>
-  </si>
-  <si>
-    <t>Arginine and Proline Metabolism</t>
-  </si>
-  <si>
-    <t>E1083,E1942</t>
-  </si>
-  <si>
-    <t>Vitamin B1 (thiamin) metabolism</t>
-  </si>
-  <si>
-    <t>E742</t>
-  </si>
-  <si>
-    <t>Vitamin E metabolism</t>
-  </si>
-  <si>
-    <t>E1488</t>
-  </si>
-  <si>
-    <t>Alanine and Aspartate Metabolism</t>
-  </si>
-  <si>
-    <t>E2159</t>
-  </si>
-  <si>
-    <t>Xenobiotics metabolism</t>
-  </si>
-  <si>
-    <t>E1662,E1437</t>
-  </si>
-  <si>
-    <t>,C00249</t>
-  </si>
-  <si>
-    <t>$Hexadecanoate (n-C16:0)</t>
-  </si>
-  <si>
-    <t>Glycine, serine, alanine and threonine metabolism</t>
-  </si>
-  <si>
-    <t>E263,E264,E2015,E265</t>
-  </si>
-  <si>
-    <t>Alkaloid biosynthesis II</t>
-  </si>
-  <si>
-    <t>E1274</t>
-  </si>
-  <si>
-    <t>Androgen and estrogen biosynthesis and metabolism</t>
-  </si>
-  <si>
-    <t>E1145,E368,E416,E148,E39,E1873,E369,E157,E1676,E85,E129</t>
-  </si>
-  <si>
-    <t>,,,,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$$$</t>
-  </si>
-  <si>
-    <t>Squalene and cholesterol biosynthesis</t>
-  </si>
-  <si>
-    <t>E2230</t>
-  </si>
-  <si>
-    <t>Purine metabolism</t>
-  </si>
-  <si>
-    <t>E2150,E240,E1950,E1735,E247,E2196,E1957</t>
-  </si>
-  <si>
-    <t>Prostaglandin formation from arachidonate</t>
-  </si>
-  <si>
-    <t>E370,E1358,E2088,E1043,E913,E1368</t>
-  </si>
-  <si>
-    <t>,,C00219,,,</t>
-  </si>
-  <si>
-    <t>$$arachidonic acid$$$</t>
-  </si>
-  <si>
-    <t>Ascorbate (Vitamin C) and Aldarate Metabolism</t>
-  </si>
-  <si>
-    <t>E267,E1725</t>
-  </si>
-  <si>
-    <t>Tryptophan metabolism</t>
-  </si>
-  <si>
-    <t>E1851,E75,E590,E396,E341,E1224,E78,E644,E508,E2027,E944,E1742,E1727,E10,E945,E1215,E988,E468,E1839,E1046,E2042,E947,E1448,E1048,E1473</t>
-  </si>
-  <si>
-    <t>,,C05638,,,,,,,,,,,,,,,C00331,CE5538/C05653,CE1918/CE5629,C05639,,,CE1918/CE5629,C00268/C02953/C04244</t>
-  </si>
-  <si>
-    <t>$$5-Hydroxykynurenamine$$$$$$$$$$$$$$$Indolepyruvate; Indolepyruvic acid; (Indol-3-yl)pyruvate; Indole-3-pyruvate; 3-(Indol-3-yl)pyruvate$noradrenochrome/N-Formylanthranilate$5-hydroxytryptophol/1,2-dehydrosalsolinol$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$$$5-hydroxytryptophol/1,2-dehydrosalsolinol$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin</t>
-  </si>
-  <si>
-    <t>Methionine and cysteine metabolism</t>
-  </si>
-  <si>
-    <t>E1083</t>
-  </si>
-  <si>
-    <t>R Group Synthesis</t>
-  </si>
-  <si>
-    <t>C5-Branched dibasic acid metabolism</t>
-  </si>
-  <si>
-    <t>Pyruvate Metabolism</t>
-  </si>
-  <si>
-    <t>Di-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
-    <t>Glycerolipid metabolism</t>
-  </si>
-  <si>
-    <t>3-oxo-10R-octadecatrienoate beta-oxidation</t>
-  </si>
-  <si>
-    <t>Glycosylphosphatidylinositol(GPI)-anchor biosynthesis</t>
-  </si>
-  <si>
-    <t>Parathio degradation</t>
-  </si>
-  <si>
-    <t>Propanoate metabolism</t>
-  </si>
-  <si>
-    <t>Electron transport chain</t>
-  </si>
-  <si>
-    <t>Vitamin H (biotin) metabolism</t>
-  </si>
-  <si>
-    <t>Heparan sulfate biosynthesis</t>
-  </si>
-  <si>
-    <t>Glycosaminoglycan degradation</t>
-  </si>
-  <si>
-    <t>Fatty acid oxidation</t>
-  </si>
-  <si>
-    <t>ROS Detoxification</t>
-  </si>
-  <si>
-    <t>Mono-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
-    <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
-  </si>
-  <si>
-    <t>Geraniol degradation</t>
-  </si>
-  <si>
-    <t>Vitamin D</t>
-  </si>
-  <si>
-    <t>Dynorphin metabolism</t>
-  </si>
-  <si>
-    <t>Fatty acid oxidation, peroxisome</t>
-  </si>
-  <si>
-    <t>Polyunsaturated fatty acid biosynthesis</t>
-  </si>
-  <si>
-    <t>TCA cycle</t>
-  </si>
-  <si>
-    <t>3-Chloroacrylic acid degradation</t>
-  </si>
-  <si>
-    <t>Sphingolipid metabolism</t>
-  </si>
-  <si>
-    <t>Proteoglycan biosynthesis</t>
-  </si>
-  <si>
-    <t>Vitamin K metabolism</t>
-  </si>
-  <si>
-    <t>Glutamate metabolism</t>
-  </si>
-  <si>
-    <t>Benzoate degradation via CoA ligation</t>
-  </si>
-  <si>
-    <t>Dimethyl-branched-chain fatty acid mitochondrial beta-oxidation</t>
-  </si>
-  <si>
-    <t>Atrazine degradation</t>
-  </si>
-  <si>
-    <t>Vitamin B12 (cyanocobalamin) metabolism</t>
-  </si>
-  <si>
-    <t>Carbon fixation</t>
-  </si>
-  <si>
-    <t>Nucleotide Sugar Metabolism</t>
-  </si>
-  <si>
-    <t>1- and 2-Methylnaphthalene degradation</t>
-  </si>
-  <si>
-    <t>Nitrogen metabolism</t>
-  </si>
-  <si>
     <t>Trihydroxycoprostanoyl-CoA beta-oxidation</t>
-  </si>
-  <si>
-    <t>Phytanic acid peroxisomal oxidation</t>
-  </si>
-  <si>
-    <t>Selenoamino acid metabolism</t>
   </si>
 </sst>
 </file>
@@ -1231,13 +1228,13 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D2">
-        <v>0.00512561969582388</v>
+        <v>0.002907514159425892</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1254,13 +1251,13 @@
         <v>11</v>
       </c>
       <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3">
         <v>10</v>
       </c>
-      <c r="C3">
-        <v>17</v>
-      </c>
       <c r="D3">
-        <v>0.005545752457776657</v>
+        <v>0.005260415791331238</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1277,13 +1274,13 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="C4">
-        <v>30</v>
+        <v>172</v>
       </c>
       <c r="D4">
-        <v>0.00604991177211999</v>
+        <v>0.007966252668022386</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1300,13 +1297,13 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>172</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>0.01848584152592219</v>
+        <v>0.009697316011495606</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1323,13 +1320,13 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>0.01949416015460886</v>
+        <v>0.01257121729046571</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1352,7 +1349,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>0.03848416099487438</v>
+        <v>0.01840305204954538</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1369,13 +1366,13 @@
         <v>31</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D8">
-        <v>0.03848416099487438</v>
+        <v>0.02359624207996504</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1392,13 +1389,13 @@
         <v>35</v>
       </c>
       <c r="B9">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>0.04192924964288716</v>
+        <v>0.02848691618628258</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1415,13 +1412,13 @@
         <v>39</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>0.05192840937736325</v>
+        <v>0.04704122619787902</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1438,13 +1435,13 @@
         <v>43</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="D11">
-        <v>0.06108730358793379</v>
+        <v>0.06423421455101595</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -1464,10 +1461,10 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D12">
-        <v>0.06789345433156878</v>
+        <v>0.06475521419808071</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
@@ -1487,10 +1484,10 @@
         <v>3</v>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13">
-        <v>0.08923619863876985</v>
+        <v>0.07255340246382413</v>
       </c>
       <c r="E13" t="s">
         <v>52</v>
@@ -1507,13 +1504,13 @@
         <v>55</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14">
-        <v>0.09242920762961096</v>
+        <v>0.07255340246382413</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -1530,13 +1527,13 @@
         <v>59</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>0.09326947315351651</v>
+        <v>0.08204904119258499</v>
       </c>
       <c r="E15" t="s">
         <v>60</v>
@@ -1553,44 +1550,50 @@
         <v>63</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D16">
-        <v>0.1153684564322326</v>
+        <v>0.08236836355691501</v>
       </c>
       <c r="E16" t="s">
-        <v>64</v>
+        <v>28</v>
+      </c>
+      <c r="F16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>0.08236836355691501</v>
+      </c>
+      <c r="E17" t="s">
         <v>65</v>
       </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>0.1153684564322326</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>66</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>67</v>
-      </c>
-      <c r="G17" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1599,21 +1602,21 @@
         <v>1</v>
       </c>
       <c r="D18">
-        <v>0.1153684564322326</v>
+        <v>0.08305742760625871</v>
       </c>
       <c r="E18" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" t="s">
         <v>70</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>71</v>
-      </c>
-      <c r="G18" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -1622,877 +1625,883 @@
         <v>1</v>
       </c>
       <c r="D19">
-        <v>0.1153684564322326</v>
+        <v>0.08305742760625871</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>0.08305742760625871</v>
+      </c>
+      <c r="E20" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" t="s">
         <v>74</v>
       </c>
-      <c r="B20">
-        <v>3</v>
-      </c>
-      <c r="C20">
-        <v>7</v>
-      </c>
-      <c r="D20">
-        <v>0.1330140324342492</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="G20" t="s">
         <v>75</v>
-      </c>
-      <c r="F20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G20" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>23</v>
+      </c>
+      <c r="D21">
+        <v>0.09198164736727114</v>
+      </c>
+      <c r="E21" t="s">
         <v>78</v>
       </c>
-      <c r="B21">
-        <v>3</v>
-      </c>
-      <c r="C21">
-        <v>7</v>
-      </c>
-      <c r="D21">
-        <v>0.1330140324342492</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>79</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>80</v>
-      </c>
-      <c r="G21" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+      <c r="C22">
+        <v>8</v>
+      </c>
+      <c r="D22">
+        <v>0.09851935261592241</v>
+      </c>
+      <c r="E22" t="s">
         <v>82</v>
       </c>
-      <c r="B22">
-        <v>2</v>
-      </c>
-      <c r="C22">
-        <v>4</v>
-      </c>
-      <c r="D22">
-        <v>0.1337702714057642</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>83</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>84</v>
-      </c>
-      <c r="G22" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23">
-        <v>0.1337702714057642</v>
+        <v>0.1346363926656695</v>
       </c>
       <c r="E23" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" t="s">
         <v>87</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>88</v>
-      </c>
-      <c r="G23" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24">
+        <v>17</v>
+      </c>
+      <c r="D24">
+        <v>0.1431236449807566</v>
+      </c>
+      <c r="E24" t="s">
         <v>90</v>
       </c>
-      <c r="B24">
-        <v>20</v>
-      </c>
-      <c r="C24">
-        <v>63</v>
-      </c>
-      <c r="D24">
-        <v>0.1422569531972103</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>91</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>92</v>
-      </c>
-      <c r="G24" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
       <c r="C25">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D25">
-        <v>0.1741030165532308</v>
+        <v>0.1434429673450866</v>
       </c>
       <c r="E25" t="s">
+        <v>94</v>
+      </c>
+      <c r="F25" t="s">
         <v>95</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>96</v>
-      </c>
-      <c r="G25" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26">
+        <v>4</v>
+      </c>
+      <c r="C26">
+        <v>13</v>
+      </c>
+      <c r="D26">
+        <v>0.1434429673450866</v>
+      </c>
+      <c r="E26" t="s">
         <v>98</v>
       </c>
-      <c r="B26">
-        <v>6</v>
-      </c>
-      <c r="C26">
-        <v>18</v>
-      </c>
-      <c r="D26">
-        <v>0.1843542559448786</v>
-      </c>
-      <c r="E26" t="s">
-        <v>99</v>
-      </c>
       <c r="F26" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="G26" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27">
+        <v>12</v>
+      </c>
+      <c r="C27">
+        <v>46</v>
+      </c>
+      <c r="D27">
+        <v>0.1448210954437741</v>
+      </c>
+      <c r="E27" t="s">
         <v>100</v>
       </c>
-      <c r="B27">
-        <v>2</v>
-      </c>
-      <c r="C27">
-        <v>5</v>
-      </c>
-      <c r="D27">
-        <v>0.1981346105369297</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>101</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>102</v>
-      </c>
-      <c r="G27" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C28">
         <v>46</v>
       </c>
       <c r="D28">
-        <v>0.2043525754138308</v>
+        <v>0.1448210954437741</v>
       </c>
       <c r="E28" t="s">
+        <v>104</v>
+      </c>
+      <c r="F28" t="s">
         <v>105</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>106</v>
-      </c>
-      <c r="G28" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29">
+        <v>7</v>
+      </c>
+      <c r="C29">
+        <v>26</v>
+      </c>
+      <c r="D29">
+        <v>0.1575771835767466</v>
+      </c>
+      <c r="E29" t="s">
         <v>108</v>
       </c>
-      <c r="B29">
-        <v>4</v>
-      </c>
-      <c r="C29">
-        <v>12</v>
-      </c>
-      <c r="D29">
-        <v>0.2116628854718091</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>109</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>110</v>
-      </c>
-      <c r="G29" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30">
+        <v>4</v>
+      </c>
+      <c r="C30">
+        <v>14</v>
+      </c>
+      <c r="D30">
+        <v>0.1657619199677316</v>
+      </c>
+      <c r="E30" t="s">
         <v>112</v>
       </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-      <c r="D30">
-        <v>0.227375850768843</v>
-      </c>
-      <c r="E30" t="s">
-        <v>64</v>
+      <c r="F30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G30" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>0.2363666918746324</v>
+        <v>0.1677450799146233</v>
       </c>
       <c r="E31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F31" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G31" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32">
+        <v>0.1677450799146233</v>
+      </c>
+      <c r="E32" t="s">
+        <v>116</v>
+      </c>
+      <c r="F32" t="s">
         <v>117</v>
       </c>
-      <c r="B32">
-        <v>12</v>
-      </c>
-      <c r="C32">
-        <v>41</v>
-      </c>
-      <c r="D32">
-        <v>0.2481304092093101</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="G32" t="s">
         <v>118</v>
-      </c>
-      <c r="F32" t="s">
-        <v>119</v>
-      </c>
-      <c r="G32" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
+        <v>120</v>
+      </c>
+      <c r="B33">
+        <v>3</v>
+      </c>
+      <c r="C33">
+        <v>10</v>
+      </c>
+      <c r="D33">
+        <v>0.1685685954857901</v>
+      </c>
+      <c r="E33" t="s">
         <v>121</v>
       </c>
-      <c r="B33">
-        <v>2</v>
-      </c>
-      <c r="C33">
-        <v>6</v>
-      </c>
-      <c r="D33">
-        <v>0.2605663389631123</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>122</v>
       </c>
-      <c r="F33" t="s">
-        <v>88</v>
-      </c>
       <c r="G33" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B34">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D34">
-        <v>0.2718258969834468</v>
+        <v>0.1713080452429371</v>
       </c>
       <c r="E34" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C35">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D35">
-        <v>0.2843458532896395</v>
+        <v>0.1836271659299844</v>
       </c>
       <c r="E35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F35" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G35" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D36">
-        <v>0.2843458532896395</v>
+        <v>0.1901480647384078</v>
       </c>
       <c r="E36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F36" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="G36" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B37">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C37">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="D37">
-        <v>0.2887152340139484</v>
+        <v>0.1901480647384078</v>
       </c>
       <c r="E37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C38">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D38">
-        <v>0.3029997479203428</v>
+        <v>0.200063864472866</v>
       </c>
       <c r="E38" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F38" t="s">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="G38" t="s">
-        <v>46</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D39">
-        <v>0.3188807663221578</v>
+        <v>0.2142316935849818</v>
       </c>
       <c r="E39" t="s">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="F39" t="s">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="G39" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D40">
-        <v>0.3188807663221578</v>
+        <v>0.2142316935849818</v>
       </c>
       <c r="E40" t="s">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="F40" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="G40" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D41">
-        <v>0.3188807663221578</v>
+        <v>0.2142316935849818</v>
       </c>
       <c r="E41" t="s">
-        <v>70</v>
+        <v>149</v>
       </c>
       <c r="F41" t="s">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="G41" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D42">
-        <v>0.3188807663221578</v>
+        <v>0.2142316935849818</v>
       </c>
       <c r="E42" t="s">
-        <v>143</v>
+        <v>153</v>
+      </c>
+      <c r="F42" t="s">
+        <v>144</v>
+      </c>
+      <c r="G42" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D43">
-        <v>0.3188807663221578</v>
+        <v>0.233945647972303</v>
       </c>
       <c r="E43" t="s">
-        <v>145</v>
+        <v>52</v>
+      </c>
+      <c r="F43" t="s">
+        <v>53</v>
+      </c>
+      <c r="G43" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D44">
-        <v>0.3188807663221578</v>
+        <v>0.2343826154182283</v>
       </c>
       <c r="E44" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="F44" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="G44" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D45">
-        <v>0.3210654566843122</v>
+        <v>0.2351725181089394</v>
       </c>
       <c r="E45" t="s">
-        <v>151</v>
+        <v>73</v>
       </c>
       <c r="F45" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G45" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D46">
-        <v>0.3210654566843122</v>
+        <v>0.2351725181089394</v>
       </c>
       <c r="E46" t="s">
-        <v>153</v>
+        <v>73</v>
       </c>
       <c r="F46" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G46" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D47">
-        <v>0.3210654566843122</v>
+        <v>0.2351725181089394</v>
       </c>
       <c r="E47" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F47" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G47" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D48">
-        <v>0.3210654566843122</v>
+        <v>0.2351725181089394</v>
       </c>
       <c r="E48" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F48" t="s">
-        <v>88</v>
+        <v>163</v>
       </c>
       <c r="G48" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49">
         <v>3</v>
       </c>
-      <c r="C49">
-        <v>11</v>
-      </c>
       <c r="D49">
-        <v>0.3261070498277456</v>
+        <v>0.2351725181089394</v>
       </c>
       <c r="E49" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="F49" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="G49" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
         <v>3</v>
       </c>
-      <c r="C50">
-        <v>11</v>
-      </c>
       <c r="D50">
-        <v>0.3261070498277456</v>
+        <v>0.2351725181089394</v>
       </c>
       <c r="E50" t="s">
-        <v>162</v>
-      </c>
-      <c r="F50" t="s">
-        <v>80</v>
-      </c>
-      <c r="G50" t="s">
-        <v>81</v>
+        <v>168</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51">
         <v>3</v>
       </c>
-      <c r="C51">
-        <v>11</v>
-      </c>
       <c r="D51">
-        <v>0.3261070498277456</v>
+        <v>0.2351725181089394</v>
       </c>
       <c r="E51" t="s">
-        <v>164</v>
-      </c>
-      <c r="F51" t="s">
-        <v>80</v>
-      </c>
-      <c r="G51" t="s">
-        <v>81</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B52">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C52">
         <v>26</v>
       </c>
       <c r="D52">
-        <v>0.3266112091420889</v>
+        <v>0.2473403808339356</v>
       </c>
       <c r="E52" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="F52" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="G52" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B53">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="D53">
-        <v>0.3280396605327283</v>
+        <v>0.2559284717903901</v>
       </c>
       <c r="E53" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F53" t="s">
-        <v>169</v>
+        <v>87</v>
       </c>
       <c r="G53" t="s">
-        <v>170</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C54">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="D54">
-        <v>0.3327451474665994</v>
+        <v>0.2675753348683215</v>
       </c>
       <c r="E54" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F54" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="G54" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C55">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D55">
-        <v>0.3390471388958911</v>
+        <v>0.2724996218550949</v>
       </c>
       <c r="E55" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="F55" t="s">
-        <v>177</v>
+        <v>122</v>
       </c>
       <c r="G55" t="s">
-        <v>178</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C56">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D56">
-        <v>0.3390471388958911</v>
+        <v>0.2919950925194534</v>
       </c>
       <c r="E56" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F56" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G56" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C57">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D57">
-        <v>0.3688765649945382</v>
+        <v>0.3120619821515605</v>
       </c>
       <c r="E57" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F57" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G57" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -2501,210 +2510,222 @@
         <v>4</v>
       </c>
       <c r="D58">
-        <v>0.4017309469792454</v>
+        <v>0.3287507772978606</v>
       </c>
       <c r="E58" t="s">
-        <v>188</v>
+        <v>116</v>
+      </c>
+      <c r="F58" t="s">
+        <v>117</v>
+      </c>
+      <c r="G58" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59">
         <v>4</v>
       </c>
-      <c r="C59">
-        <v>17</v>
-      </c>
       <c r="D59">
-        <v>0.4302159482396437</v>
+        <v>0.3287507772978606</v>
       </c>
       <c r="E59" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F59" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G59" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D60">
-        <v>0.432820771363751</v>
+        <v>0.3287507772978606</v>
       </c>
       <c r="E60" t="s">
-        <v>191</v>
-      </c>
-      <c r="F60" t="s">
-        <v>80</v>
-      </c>
-      <c r="G60" t="s">
-        <v>81</v>
+        <v>194</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C61">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D61">
-        <v>0.432820771363751</v>
+        <v>0.3287507772978606</v>
       </c>
       <c r="E61" t="s">
-        <v>193</v>
+        <v>116</v>
       </c>
       <c r="F61" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="G61" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C62">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D62">
-        <v>0.4466851525081926</v>
+        <v>0.3399774793700946</v>
       </c>
       <c r="E62" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F62" t="s">
-        <v>88</v>
+        <v>198</v>
       </c>
       <c r="G62" t="s">
-        <v>89</v>
+        <v>199</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B63">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C63">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D63">
-        <v>0.4661793126628014</v>
+        <v>0.3399774793700946</v>
       </c>
       <c r="E63" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F63" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G63" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B64">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D64">
-        <v>0.5037391815813798</v>
+        <v>0.3661955261256113</v>
       </c>
       <c r="E64" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F64" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G64" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C65">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D65">
-        <v>0.5100411730106714</v>
+        <v>0.3750021008050285</v>
       </c>
       <c r="E65" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F65" t="s">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="G65" t="s">
-        <v>81</v>
+        <v>211</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
       <c r="C66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D66">
-        <v>0.5227291824216452</v>
+        <v>0.3819599670593771</v>
       </c>
       <c r="E66" t="s">
-        <v>207</v>
+        <v>116</v>
+      </c>
+      <c r="F66" t="s">
+        <v>117</v>
+      </c>
+      <c r="G66" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C67">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="D67">
-        <v>0.5227291824216452</v>
+        <v>0.3990353103309188</v>
       </c>
       <c r="E67" t="s">
-        <v>209</v>
+        <v>214</v>
+      </c>
+      <c r="F67" t="s">
+        <v>215</v>
+      </c>
+      <c r="G67" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B68">
         <v>2</v>
@@ -2713,152 +2734,164 @@
         <v>11</v>
       </c>
       <c r="D68">
-        <v>0.5234013948407696</v>
+        <v>0.401573082805331</v>
       </c>
       <c r="E68" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="F68" t="s">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="G68" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D69">
-        <v>0.5576842282161163</v>
+        <v>0.401573082805331</v>
       </c>
       <c r="E69" t="s">
-        <v>213</v>
+        <v>220</v>
+      </c>
+      <c r="F69" t="s">
+        <v>144</v>
+      </c>
+      <c r="G69" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D70">
-        <v>0.5576842282161163</v>
+        <v>0.4230012940958975</v>
       </c>
       <c r="E70" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D71">
-        <v>0.5576842282161163</v>
+        <v>0.4289003546158888</v>
       </c>
       <c r="E71" t="s">
-        <v>217</v>
+        <v>125</v>
+      </c>
+      <c r="F71" t="s">
+        <v>126</v>
+      </c>
+      <c r="G71" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D72">
-        <v>0.5756659104276951</v>
+        <v>0.4592023663467841</v>
       </c>
       <c r="E72" t="s">
-        <v>219</v>
+        <v>73</v>
       </c>
       <c r="F72" t="s">
-        <v>220</v>
+        <v>74</v>
       </c>
       <c r="G72" t="s">
-        <v>221</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D73">
-        <v>0.5857490967145618</v>
+        <v>0.4592023663467841</v>
       </c>
       <c r="E73" t="s">
-        <v>223</v>
+        <v>116</v>
       </c>
       <c r="F73" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="G73" t="s">
-        <v>46</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D74">
-        <v>0.5878497605243257</v>
+        <v>0.5169324885296045</v>
       </c>
       <c r="E74" t="s">
-        <v>225</v>
+        <v>227</v>
+      </c>
+      <c r="F74" t="s">
+        <v>122</v>
+      </c>
+      <c r="G74" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B75">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="D75">
-        <v>0.5878497605243257</v>
+        <v>0.5367136686778373</v>
       </c>
       <c r="E75" t="s">
-        <v>227</v>
-      </c>
-      <c r="F75" t="s">
-        <v>228</v>
-      </c>
-      <c r="G75" t="s">
         <v>229</v>
       </c>
     </row>
@@ -2873,7 +2906,7 @@
         <v>9</v>
       </c>
       <c r="D76">
-        <v>0.6173430804134107</v>
+        <v>0.5367136686778373</v>
       </c>
       <c r="E76" t="s">
         <v>231</v>
@@ -2884,310 +2917,352 @@
         <v>232</v>
       </c>
       <c r="B77">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D77">
-        <v>0.6296109570624318</v>
+        <v>0.5584275894522781</v>
       </c>
       <c r="E77" t="s">
-        <v>233</v>
+        <v>116</v>
       </c>
       <c r="F77" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G77" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B78">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D78">
-        <v>0.6338963112343501</v>
+        <v>0.5594863951866356</v>
       </c>
       <c r="E78" t="s">
-        <v>235</v>
+        <v>125</v>
       </c>
       <c r="F78" t="s">
-        <v>236</v>
+        <v>126</v>
       </c>
       <c r="G78" t="s">
-        <v>237</v>
+        <v>127</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D79">
-        <v>0.6757415343248466</v>
+        <v>0.571301322666846</v>
       </c>
       <c r="E79" t="s">
-        <v>239</v>
+        <v>162</v>
       </c>
       <c r="F79" t="s">
-        <v>88</v>
+        <v>163</v>
       </c>
       <c r="G79" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B80">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C80">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="D80">
-        <v>0.684564322325855</v>
+        <v>0.5713517419875296</v>
       </c>
       <c r="E80" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F80" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="G80" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81">
         <v>19</v>
       </c>
       <c r="D81">
-        <v>0.6870851188975716</v>
+        <v>0.5810322515587973</v>
       </c>
       <c r="E81" t="s">
+        <v>240</v>
+      </c>
+      <c r="F81" t="s">
+        <v>87</v>
+      </c>
+      <c r="G81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" t="s">
+        <v>241</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82">
+        <v>12</v>
+      </c>
+      <c r="D82">
+        <v>0.5845616040066554</v>
+      </c>
+      <c r="E82" t="s">
+        <v>73</v>
+      </c>
+      <c r="F82" t="s">
+        <v>74</v>
+      </c>
+      <c r="G82" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" t="s">
+        <v>242</v>
+      </c>
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83">
+        <v>13</v>
+      </c>
+      <c r="D83">
+        <v>0.5970151762155258</v>
+      </c>
+      <c r="E83" t="s">
+        <v>69</v>
+      </c>
+      <c r="F83" t="s">
+        <v>70</v>
+      </c>
+      <c r="G83" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" t="s">
+        <v>243</v>
+      </c>
+      <c r="B84">
+        <v>21</v>
+      </c>
+      <c r="C84">
+        <v>130</v>
+      </c>
+      <c r="D84">
+        <v>0.6205105796541235</v>
+      </c>
+      <c r="E84" t="s">
+        <v>244</v>
+      </c>
+      <c r="F84" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" t="s">
+      <c r="G84" t="s">
         <v>246</v>
       </c>
-      <c r="B82">
-        <v>0</v>
-      </c>
-      <c r="C82">
-        <v>0</v>
-      </c>
-      <c r="D82">
-        <v>0.6910343668599277</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" t="s">
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" t="s">
         <v>247</v>
       </c>
-      <c r="B83">
-        <v>0</v>
-      </c>
-      <c r="C83">
+      <c r="B85">
+        <v>4</v>
+      </c>
+      <c r="C85">
+        <v>39</v>
+      </c>
+      <c r="D85">
+        <v>0.6299053797415169</v>
+      </c>
+      <c r="E85" t="s">
+        <v>248</v>
+      </c>
+      <c r="F85" t="s">
+        <v>66</v>
+      </c>
+      <c r="G85" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" t="s">
+        <v>249</v>
+      </c>
+      <c r="B86">
+        <v>0</v>
+      </c>
+      <c r="C86">
+        <v>7</v>
+      </c>
+      <c r="D86">
+        <v>0.6461740138821196</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" t="s">
+        <v>250</v>
+      </c>
+      <c r="B87">
+        <v>0</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>0.6461740138821196</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" t="s">
+        <v>251</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+      <c r="C88">
         <v>2</v>
       </c>
-      <c r="D83">
-        <v>0.6910343668599277</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" t="s">
-        <v>248</v>
-      </c>
-      <c r="B84">
-        <v>0</v>
-      </c>
-      <c r="C84">
+      <c r="D88">
+        <v>0.6461740138821196</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" t="s">
+        <v>252</v>
+      </c>
+      <c r="B89">
+        <v>0</v>
+      </c>
+      <c r="C89">
         <v>1</v>
       </c>
-      <c r="D84">
-        <v>0.6910343668599277</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" t="s">
-        <v>249</v>
-      </c>
-      <c r="B85">
-        <v>0</v>
-      </c>
-      <c r="C85">
-        <v>4</v>
-      </c>
-      <c r="D85">
-        <v>0.6910343668599277</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" t="s">
-        <v>250</v>
-      </c>
-      <c r="B86">
-        <v>0</v>
-      </c>
-      <c r="C86">
-        <v>0</v>
-      </c>
-      <c r="D86">
-        <v>0.6910343668599277</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" t="s">
-        <v>251</v>
-      </c>
-      <c r="B87">
-        <v>0</v>
-      </c>
-      <c r="C87">
+      <c r="D89">
+        <v>0.6461740138821196</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" t="s">
+        <v>253</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+      <c r="C90">
+        <v>2</v>
+      </c>
+      <c r="D90">
+        <v>0.6461740138821196</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" t="s">
+        <v>254</v>
+      </c>
+      <c r="B91">
+        <v>0</v>
+      </c>
+      <c r="C91">
+        <v>6</v>
+      </c>
+      <c r="D91">
+        <v>0.6461740138821196</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" t="s">
+        <v>255</v>
+      </c>
+      <c r="B92">
+        <v>0</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+      <c r="D92">
+        <v>0.6461740138821196</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" t="s">
+        <v>256</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+      <c r="C93">
         <v>11</v>
       </c>
-      <c r="D87">
-        <v>0.6910343668599277</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" t="s">
-        <v>252</v>
-      </c>
-      <c r="B88">
-        <v>0</v>
-      </c>
-      <c r="C88">
-        <v>0</v>
-      </c>
-      <c r="D88">
-        <v>0.6910343668599277</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" t="s">
-        <v>253</v>
-      </c>
-      <c r="B89">
-        <v>0</v>
-      </c>
-      <c r="C89">
-        <v>0</v>
-      </c>
-      <c r="D89">
-        <v>0.6910343668599277</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" t="s">
-        <v>254</v>
-      </c>
-      <c r="B90">
-        <v>0</v>
-      </c>
-      <c r="C90">
-        <v>5</v>
-      </c>
-      <c r="D90">
-        <v>0.6910343668599277</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" t="s">
-        <v>255</v>
-      </c>
-      <c r="B91">
-        <v>0</v>
-      </c>
-      <c r="C91">
-        <v>3</v>
-      </c>
-      <c r="D91">
-        <v>0.6910343668599277</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" t="s">
-        <v>256</v>
-      </c>
-      <c r="B92">
-        <v>0</v>
-      </c>
-      <c r="C92">
-        <v>5</v>
-      </c>
-      <c r="D92">
-        <v>0.6910343668599277</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" t="s">
+      <c r="D93">
+        <v>0.6461740138821196</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" t="s">
         <v>257</v>
       </c>
-      <c r="B93">
-        <v>0</v>
-      </c>
-      <c r="C93">
-        <v>0</v>
-      </c>
-      <c r="D93">
-        <v>0.6910343668599277</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" t="s">
+      <c r="B94">
+        <v>0</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+      <c r="D94">
+        <v>0.6461740138821196</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" t="s">
         <v>258</v>
       </c>
-      <c r="B94">
-        <v>0</v>
-      </c>
-      <c r="C94">
-        <v>0</v>
-      </c>
-      <c r="D94">
-        <v>0.6910343668599277</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" t="s">
+      <c r="B95">
+        <v>0</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="D95">
+        <v>0.6461740138821196</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" t="s">
         <v>259</v>
       </c>
-      <c r="B95">
-        <v>0</v>
-      </c>
-      <c r="C95">
-        <v>3</v>
-      </c>
-      <c r="D95">
-        <v>0.6910343668599277</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" t="s">
-        <v>260</v>
-      </c>
       <c r="B96">
         <v>0</v>
       </c>
@@ -3195,40 +3270,40 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B98">
         <v>0</v>
       </c>
       <c r="C98">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D98">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -3237,12 +3312,12 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -3251,12 +3326,12 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -3265,12 +3340,12 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -3279,40 +3354,40 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B103">
         <v>0</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D103">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B104">
         <v>0</v>
       </c>
       <c r="C104">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -3321,12 +3396,12 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -3335,12 +3410,12 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -3349,54 +3424,54 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B108">
         <v>0</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B109">
         <v>0</v>
       </c>
       <c r="C109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D109">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B110">
         <v>0</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D110">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -3405,12 +3480,12 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -3419,40 +3494,40 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B113">
         <v>0</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B114">
         <v>0</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D114">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -3461,12 +3536,12 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -3475,12 +3550,12 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -3489,12 +3564,12 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -3503,35 +3578,35 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B119">
         <v>0</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D119">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B120">
         <v>0</v>
       </c>
       <c r="C120">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D120">
-        <v>0.6910343668599277</v>
+        <v>0.6461740138821196</v>
       </c>
     </row>
   </sheetData>
